--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_191_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_191_R20.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0408</v>
+        <v>5.4104</v>
       </c>
       <c r="E2" t="n">
         <v>5.6125</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5717</v>
+        <v>-0.202</v>
       </c>
       <c r="G2" t="n">
         <v>4.9976</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4195</v>
+        <v>0.7892</v>
       </c>
       <c r="T2" t="n">
         <v>0.4876</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.3016</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8242</v>
+        <v>2.5355</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7321</v>
+        <v>2.1077</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0921</v>
+        <v>0.4278</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5205</v>
+        <v>1.2625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.39</v>
+        <v>1.4801</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1305</v>
+        <v>-0.2176</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6179</v>
+        <v>2.9172</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1161</v>
+        <v>2.1846</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5018</v>
+        <v>0.7326</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0974</v>
+        <v>-1.6547</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7261</v>
+        <v>-0.7045</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3713</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3759</v>
+        <v>0.6673</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1142</v>
+        <v>0.4404</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2617</v>
+        <v>0.2269</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9709</v>
+        <v>2.3702</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0373</v>
+        <v>1.6142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9336</v>
+        <v>0.756</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6198</v>
+        <v>0.5205</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9075</v>
+        <v>0.39</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2877</v>
+        <v>0.1305</v>
       </c>
       <c r="J4" t="n">
-        <v>1.928</v>
+        <v>1.6179</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6336</v>
+        <v>1.1161</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2944</v>
+        <v>0.5018</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3082</v>
+        <v>-1.0974</v>
       </c>
       <c r="N4" t="n">
         <v>-0.7261</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5821</v>
+        <v>-0.3713</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1681</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1246</v>
+        <v>-0.0037</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0435</v>
+        <v>0.9256</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6468</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9353</v>
+        <v>2.1212</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4669</v>
+        <v>0.8208</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4684</v>
+        <v>1.3004</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0165</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3282</v>
+        <v>0.514</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1494</v>
+        <v>0.2045</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4775</v>
+        <v>0.3095</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8449</v>
+        <v>1.9431</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5179</v>
+        <v>1.2923</v>
       </c>
       <c r="F6" t="n">
-        <v>0.327</v>
+        <v>0.6508</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2625</v>
+        <v>0.0558</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4801</v>
+        <v>-2.7215</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2176</v>
+        <v>2.7772</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9172</v>
+        <v>1.6179</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1846</v>
+        <v>-1.9522</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7326</v>
+        <v>3.5701</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6547</v>
+        <v>-1.5621</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7045</v>
+        <v>-0.7692</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.7929</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0233</v>
+        <v>0.3539</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>-0.3771</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1261</v>
+        <v>0.731</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0.2836</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7922</v>
+        <v>1.4819</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4103</v>
+        <v>0.4475</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3819</v>
+        <v>1.0344</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0558</v>
+        <v>0.6198</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7215</v>
+        <v>0.9075</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7772</v>
+        <v>-0.2877</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6179</v>
+        <v>1.928</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9522</v>
+        <v>1.6336</v>
       </c>
       <c r="L8" t="n">
-        <v>3.5701</v>
+        <v>0.2944</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5621</v>
+        <v>-1.3082</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7692</v>
+        <v>-0.7261</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7929</v>
+        <v>-0.5821</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.203</v>
+        <v>0.6792</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2592</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4621</v>
+        <v>0.1443</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>0.6468</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2836</v>
+        <v>0.5361</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4311</v>
+        <v>1.0107</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1634</v>
+        <v>-0.2814</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5946</v>
+        <v>1.2921</v>
       </c>
       <c r="G9" t="n">
         <v>2.1204</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1663</v>
+        <v>0.7459</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5623</v>
+        <v>0.4443</v>
       </c>
       <c r="U9" t="n">
-        <v>0.604</v>
+        <v>0.3016</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2759</v>
+        <v>0.6189</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0058</v>
+        <v>1.416</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7299</v>
+        <v>-0.7971</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3059</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4374</v>
+        <v>0.7804</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4525</v>
+        <v>-0.1373</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9849</v>
+        <v>0.9177</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2607</v>
+        <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1766</v>
+        <v>-0.2946</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4374</v>
+        <v>0.5046</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3385</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3673</v>
+        <v>0.3165</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3339</v>
+        <v>-0.4518</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.7683</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4057</v>
+        <v>-1.7316</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8045</v>
+        <v>-0.0968</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6012</v>
+        <v>-1.6348</v>
       </c>
       <c r="G12" t="n">
         <v>0.8824</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2702</v>
+        <v>0.4039</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1202</v>
+        <v>-0.4125</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8501</v>
+        <v>0.8164</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9304</v>
@@ -1426,10 +1426,10 @@
         <v>17.8046</v>
       </c>
       <c r="E13" t="n">
-        <v>14.6195</v>
+        <v>14.6194</v>
       </c>
       <c r="F13" t="n">
-        <v>3.185300000000001</v>
+        <v>3.1853</v>
       </c>
       <c r="G13" t="n">
         <v>10.5602</v>
@@ -1471,10 +1471,10 @@
         <v>6.1722</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7290999999999999</v>
+        <v>0.7292000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>5.442900000000001</v>
+        <v>5.4429</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9091</v>
+        <v>0.4709</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.1618</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2755</v>
+        <v>0.3091</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2142</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6594</v>
+        <v>0.2212</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7943</v>
+        <v>0.3224</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1152</v>
+        <v>0.0528</v>
       </c>
       <c r="E15" t="n">
         <v>2.4337</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5489</v>
+        <v>-2.3809</v>
       </c>
       <c r="G15" t="n">
         <v>2.3084</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4958</v>
+        <v>-1.3278</v>
       </c>
       <c r="T15" t="n">
         <v>-1.0376</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4582</v>
+        <v>-0.2902</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5694</v>
+        <v>-0.1318</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1136</v>
+        <v>0.3495</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.4813</v>
       </c>
       <c r="G16" t="n">
         <v>1.8603</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0174</v>
+        <v>-0.5799</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4946</v>
+        <v>-0.293</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2525</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6523</v>
+        <v>-0.7532</v>
       </c>
       <c r="E17" t="n">
         <v>1.8036</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4559</v>
+        <v>-2.5567</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0591</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.539</v>
+        <v>-0.6398</v>
       </c>
       <c r="T17" t="n">
         <v>-0.7468</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V17" t="n">
         <v>-1.214</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-1.0919</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1785</v>
+        <v>0.8247</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8494</v>
+        <v>-1.9166</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9406</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0378</v>
+        <v>-0.3833</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2794</v>
+        <v>-0.0745</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2416</v>
+        <v>-0.3088</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9991</v>
+        <v>-1.1335</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0958</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9033</v>
+        <v>-1.0378</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5252</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2838</v>
+        <v>0.1494</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.343</v>
+        <v>-1.337</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5575</v>
+        <v>-1.8071</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9005</v>
+        <v>0.4701</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1943</v>
+        <v>-1.6849</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8897</v>
+        <v>0.0517</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0841</v>
+        <v>-1.7366</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1441</v>
+        <v>0.2448</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0166</v>
+        <v>0.1379</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1275</v>
+        <v>0.1069</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.3384</v>
+        <v>-1.9298</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1269</v>
+        <v>-0.0862</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.2116</v>
+        <v>-1.8435</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.6237</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3084</v>
+        <v>-0.3479</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.963</v>
+        <v>-0.4283</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6546</v>
+        <v>0.0804</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7746</v>
+        <v>-1.6283</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0431</v>
+        <v>0.6755</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2685</v>
+        <v>-2.3038</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6849</v>
+        <v>-0.1943</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0517</v>
+        <v>0.8897</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7366</v>
+        <v>-1.0841</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2448</v>
+        <v>3.1441</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1379</v>
+        <v>2.0166</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1069</v>
+        <v>1.1275</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9298</v>
+        <v>-3.3384</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0862</v>
+        <v>-1.1269</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8435</v>
+        <v>-2.2116</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.6237</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7855</v>
+        <v>-0.5937</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6642</v>
+        <v>-0.845</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1212</v>
+        <v>0.2513</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6809</v>
+        <v>-2.3778</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7668</v>
+        <v>-1.5309</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9141</v>
+        <v>-0.8469</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8004</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2722</v>
+        <v>-0.9691</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>-0.5109</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5254</v>
+        <v>-0.4582</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6913</v>
+        <v>-4.8593</v>
       </c>
       <c r="E23" t="n">
         <v>-3.9776</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7137</v>
+        <v>-0.8818</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6435</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1199</v>
+        <v>-0.288</v>
       </c>
       <c r="T23" t="n">
         <v>-0.6563</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2171</v>
+        <v>-5.0155</v>
       </c>
       <c r="E24" t="n">
         <v>-2.1643</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0528</v>
+        <v>-2.8512</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6667</v>
@@ -2326,13 +2326,13 @@
         <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4655</v>
+        <v>-1.2639</v>
       </c>
       <c r="T24" t="n">
         <v>-1.0297</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4358</v>
+        <v>-0.2341</v>
       </c>
       <c r="V24" t="n">
         <v>2.5387</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.8047</v>
+        <v>-17.8046</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3271</v>
+        <v>-3.3269</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.4776</v>
+        <v>-14.4778</v>
       </c>
       <c r="G25" t="n">
         <v>-10.5602</v>
@@ -2404,13 +2404,13 @@
         <v>17.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.1721</v>
+        <v>-6.1722</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.442900000000001</v>
+        <v>-5.443000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7290999999999999</v>
+        <v>-0.7291</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
